--- a/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Nhập kho/Tháng 07/NKSX_VNSH03_060726.xlsx
+++ b/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Nhập kho/Tháng 07/NKSX_VNSH03_060726.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\2. Báo cáo - giấy tờ\3. Sản xuất\Xuất Nhập Kho 2026\Nhập kho\Tháng 07\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12358299-9ECE-4CB0-8692-2192202AECC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04E377CF-7E89-43E1-997B-C3A9A404E898}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Nhập kho/Tháng 07/NKSX_VNSH03_060726.xlsx
+++ b/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Nhập kho/Tháng 07/NKSX_VNSH03_060726.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\2. Báo cáo - giấy tờ\3. Sản xuất\Xuất Nhập Kho 2026\Nhập kho\Tháng 07\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04E377CF-7E89-43E1-997B-C3A9A404E898}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AEB7A57-5AEE-4960-8ECB-EAA0C0F2E31D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -365,7 +365,7 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -384,6 +384,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="15">
     <border>
@@ -558,7 +564,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -739,6 +745,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1726,7 +1738,7 @@
       <c r="A30" s="36">
         <v>29</v>
       </c>
-      <c r="B30" s="41" t="s">
+      <c r="B30" s="64" t="s">
         <v>58</v>
       </c>
     </row>
@@ -1734,7 +1746,7 @@
       <c r="A31" s="36">
         <v>30</v>
       </c>
-      <c r="B31" s="41" t="s">
+      <c r="B31" s="64" t="s">
         <v>59</v>
       </c>
     </row>
@@ -1742,7 +1754,7 @@
       <c r="A32" s="36">
         <v>31</v>
       </c>
-      <c r="B32" s="41" t="s">
+      <c r="B32" s="63" t="s">
         <v>60</v>
       </c>
     </row>
@@ -1750,7 +1762,7 @@
       <c r="A33" s="36">
         <v>32</v>
       </c>
-      <c r="B33" s="41" t="s">
+      <c r="B33" s="63" t="s">
         <v>61</v>
       </c>
     </row>
@@ -1758,7 +1770,7 @@
       <c r="A34" s="36">
         <v>33</v>
       </c>
-      <c r="B34" s="41" t="s">
+      <c r="B34" s="63" t="s">
         <v>62</v>
       </c>
     </row>
@@ -1766,7 +1778,7 @@
       <c r="A35" s="36">
         <v>34</v>
       </c>
-      <c r="B35" s="41" t="s">
+      <c r="B35" s="63" t="s">
         <v>63</v>
       </c>
     </row>
@@ -1774,7 +1786,7 @@
       <c r="A36" s="36">
         <v>35</v>
       </c>
-      <c r="B36" s="41" t="s">
+      <c r="B36" s="63" t="s">
         <v>64</v>
       </c>
     </row>
@@ -1782,7 +1794,7 @@
       <c r="A37" s="36">
         <v>36</v>
       </c>
-      <c r="B37" s="41" t="s">
+      <c r="B37" s="63" t="s">
         <v>65</v>
       </c>
     </row>
@@ -1790,7 +1802,7 @@
       <c r="A38" s="36">
         <v>37</v>
       </c>
-      <c r="B38" s="41" t="s">
+      <c r="B38" s="63" t="s">
         <v>66</v>
       </c>
     </row>
@@ -1798,7 +1810,7 @@
       <c r="A39" s="36">
         <v>38</v>
       </c>
-      <c r="B39" s="41" t="s">
+      <c r="B39" s="63" t="s">
         <v>67</v>
       </c>
     </row>
@@ -1806,7 +1818,7 @@
       <c r="A40" s="36">
         <v>39</v>
       </c>
-      <c r="B40" s="41" t="s">
+      <c r="B40" s="63" t="s">
         <v>68</v>
       </c>
     </row>
@@ -1814,7 +1826,7 @@
       <c r="A41" s="36">
         <v>40</v>
       </c>
-      <c r="B41" s="41" t="s">
+      <c r="B41" s="63" t="s">
         <v>69</v>
       </c>
     </row>
